--- a/amazon_sku_listado.xlsx
+++ b/amazon_sku_listado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be230b8ca95fc96a/Inova/09 - Update automation/Datasets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be230b8ca95fc96a/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_981C14D6EDE754FFC01E13CAC4173B2B3805E126" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAEFED78-2DCD-4F72-B22E-AB073681FEAC}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_981C14D6EDE754FFC01E13CAC4173B2B3805E126" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1942DFEB-CEBA-4692-A6CB-B12F81C21D13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="335">
   <si>
     <t>ASIN</t>
   </si>
@@ -1035,13 +1035,40 @@
   </si>
   <si>
     <t>E3-CWG6-5J49</t>
+  </si>
+  <si>
+    <t>B07GT9ZXBG</t>
+  </si>
+  <si>
+    <t>Eagle Eyes 3 en 1</t>
+  </si>
+  <si>
+    <t>Eagle Eyes 3 en 1 Fit On Supersight, Juego de gafas de clip 3 en 1, lentes de día, noche y luz digital</t>
+  </si>
+  <si>
+    <t>O8-F9LI-392A</t>
+  </si>
+  <si>
+    <t>EAGLE EYES</t>
+  </si>
+  <si>
+    <t>B0FDK8V72W</t>
+  </si>
+  <si>
+    <t>Eagle Eyes Lentes de Sol Jet Silver Flash</t>
+  </si>
+  <si>
+    <t>Eagle Eyes Lentes de Sol Jet Silver Flash, Estilo Aviador, Triple Polarizado, Protección UV y Luz Azul</t>
+  </si>
+  <si>
+    <t>WB-B6M2-3D6S</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1082,6 +1109,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF232F3E"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1169,7 +1202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1240,6 +1273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1579,7 +1613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
@@ -1774,45 +1808,45 @@
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>145</v>
+      <c r="A10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" t="s">
+        <v>330</v>
+      </c>
+      <c r="F10" t="s">
+        <v>144</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="A11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="E11" t="s">
+        <v>330</v>
+      </c>
+      <c r="F11" t="s">
         <v>144</v>
       </c>
       <c r="G11" s="13" t="s">
@@ -1821,22 +1855,22 @@
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>152</v>
@@ -1844,16 +1878,16 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
@@ -1867,14 +1901,16 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="13"/>
+        <v>94</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="C14" s="13" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
@@ -1888,14 +1924,16 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" s="13"/>
+        <v>80</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="C15" s="13" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
@@ -1908,13 +1946,15 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14" t="s">
-        <v>200</v>
+      <c r="A16" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>18</v>
@@ -1925,15 +1965,15 @@
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14" t="s">
-        <v>204</v>
+      <c r="A17" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>18</v>
@@ -1945,16 +1985,12 @@
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>237</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>18</v>
@@ -1966,16 +2002,14 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>249</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>18</v>
@@ -1987,16 +2021,16 @@
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>18</v>
@@ -2008,16 +2042,16 @@
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
-        <v>258</v>
+        <v>14</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>18</v>
@@ -2029,16 +2063,16 @@
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>18</v>
@@ -2050,16 +2084,16 @@
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
-        <v>209</v>
+        <v>258</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>18</v>
@@ -2070,13 +2104,17 @@
       <c r="G23" s="14"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15" t="s">
-        <v>295</v>
+      <c r="A24" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>259</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>18</v>
@@ -2087,13 +2125,17 @@
       <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15" t="s">
-        <v>297</v>
+      <c r="A25" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>263</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>18</v>
@@ -2104,17 +2146,13 @@
       <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="D26" s="14">
-        <v>897666001256</v>
+      <c r="A26" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15" t="s">
+        <v>295</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>18</v>
@@ -2125,18 +2163,16 @@
       <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>214</v>
-      </c>
+      <c r="A27" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B27" s="14"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="14" t="s">
-        <v>205</v>
+      <c r="D27" s="15" t="s">
+        <v>297</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>144</v>
@@ -2144,20 +2180,20 @@
       <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>53</v>
+      <c r="A28" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D28" s="14">
+        <v>897666001256</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>144</v>
@@ -2168,70 +2204,71 @@
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>214</v>
+      </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="14" t="s">
+      <c r="F31" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B32" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14" t="s">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14" t="s">
         <v>227</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" t="s">
-        <v>231</v>
-      </c>
-      <c r="D31" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>24</v>
@@ -2244,15 +2281,16 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="14" t="s">
+      <c r="A33" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="B33" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F33" s="7" t="s">
@@ -2263,65 +2301,61 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="F34" s="20" t="s">
+      <c r="A34" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>144</v>
       </c>
       <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>48</v>
+      <c r="A35" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14" t="s">
+        <v>197</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>145</v>
+      <c r="A36" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>157</v>
@@ -2329,16 +2363,16 @@
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>49</v>
@@ -2352,16 +2386,16 @@
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>49</v>
@@ -2374,11 +2408,17 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14" t="s">
-        <v>194</v>
+      <c r="A39" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>49</v>
@@ -2389,13 +2429,17 @@
       <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14" t="s">
-        <v>199</v>
+      <c r="A40" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>49</v>
@@ -2406,15 +2450,11 @@
       <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>113</v>
-      </c>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>49</v>
@@ -2425,15 +2465,13 @@
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>234</v>
-      </c>
+      <c r="A42" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>49</v>
@@ -2444,15 +2482,15 @@
       <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="14" t="s">
-        <v>245</v>
+      <c r="A43" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>49</v>
@@ -2463,17 +2501,15 @@
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="15" t="s">
         <v>98</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>100</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C44" s="14"/>
       <c r="D44" s="14" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>49</v>
@@ -2485,16 +2521,14 @@
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
-        <v>45</v>
+        <v>245</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>47</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C45" s="14"/>
       <c r="D45" s="14" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>49</v>
@@ -2505,14 +2539,17 @@
       <c r="G45" s="14"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="B46" t="s">
-        <v>269</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>267</v>
+      <c r="A46" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>260</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>49</v>
@@ -2523,11 +2560,17 @@
       <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>298</v>
-      </c>
-      <c r="D47" t="s">
-        <v>299</v>
+      <c r="A47" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>264</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>49</v>
@@ -2539,14 +2582,14 @@
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>217</v>
+      <c r="A48" s="16" t="s">
+        <v>268</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
-      </c>
-      <c r="D48" t="s">
-        <v>218</v>
+        <v>269</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>267</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>49</v>
@@ -2557,13 +2600,10 @@
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>220</v>
-      </c>
-      <c r="B49" t="s">
-        <v>219</v>
+        <v>298</v>
       </c>
       <c r="D49" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>49</v>
@@ -2573,17 +2613,14 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>61</v>
+      <c r="A50" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" t="s">
+        <v>216</v>
+      </c>
+      <c r="D50" t="s">
+        <v>218</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>49</v>
@@ -2596,17 +2633,16 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="11" t="s">
+      <c r="A51" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" t="s">
+        <v>221</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F51" s="7" t="s">
@@ -2618,19 +2654,19 @@
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" s="17">
-        <v>853000000000</v>
+        <v>60</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>145</v>
@@ -2643,44 +2679,57 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="A53" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D53" t="s">
+      <c r="B54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="17">
+        <v>853000000000</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" t="s">
         <v>192</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D55" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F55" s="7" t="s">
@@ -2692,69 +2741,60 @@
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D58" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
+      <c r="E58" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D59" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F59" s="7" t="s">
@@ -2767,54 +2807,54 @@
         <v>145</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D62" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" t="s">
-        <v>225</v>
-      </c>
-      <c r="D61" t="s">
-        <v>224</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>208</v>
-      </c>
-      <c r="B62" t="s">
-        <v>229</v>
-      </c>
-      <c r="D62" t="s">
-        <v>226</v>
-      </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F62" s="7" t="s">
@@ -2826,57 +2866,59 @@
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" t="s">
+        <v>224</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>208</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B64" t="s">
+        <v>229</v>
+      </c>
+      <c r="D64" t="s">
+        <v>226</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>208</v>
+      </c>
+      <c r="B65" t="s">
         <v>212</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D65" t="s">
         <v>203</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="E65" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>182</v>
@@ -2888,22 +2930,18 @@
         <v>303</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E66" s="5" t="s">
+    <row r="66" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>180</v>
@@ -2917,16 +2955,14 @@
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B67" s="4"/>
       <c r="C67" s="4" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>9</v>
@@ -2946,19 +2982,19 @@
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="7" t="s">
         <v>144</v>
       </c>
       <c r="G68" s="4" t="s">
@@ -2973,19 +3009,21 @@
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" s="4"/>
+        <v>123</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="C69" s="4" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="7" t="s">
         <v>144</v>
       </c>
       <c r="G69" s="4" t="s">
@@ -3000,18 +3038,16 @@
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B70" s="4"/>
       <c r="C70" s="4" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E70" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -3029,18 +3065,16 @@
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B71" s="4"/>
       <c r="C71" s="4" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E71" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E71" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -3057,19 +3091,22 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B72" t="s">
-        <v>118</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>240</v>
+      <c r="A72" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="4" t="s">
         <v>144</v>
       </c>
       <c r="H72" t="s">
@@ -3080,19 +3117,22 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>242</v>
-      </c>
-      <c r="B73" t="s">
-        <v>241</v>
-      </c>
-      <c r="D73" t="s">
-        <v>243</v>
+      <c r="A73" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="4" t="s">
         <v>144</v>
       </c>
       <c r="H73" t="s">
@@ -3103,17 +3143,14 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>13</v>
+      <c r="A74" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B74" t="s">
+        <v>118</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>240</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>9</v>
@@ -3132,17 +3169,14 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>13</v>
+      <c r="A75" t="s">
+        <v>242</v>
+      </c>
+      <c r="B75" t="s">
+        <v>241</v>
+      </c>
+      <c r="D75" t="s">
+        <v>243</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>9</v>
@@ -3160,18 +3194,18 @@
         <v>305</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>9</v>
@@ -3189,14 +3223,20 @@
         <v>305</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E77" s="3" t="s">
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F77" s="7" t="s">
@@ -3212,20 +3252,20 @@
         <v>305</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E78" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F78" s="7" t="s">
@@ -3241,20 +3281,14 @@
         <v>306</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E79" s="10" t="s">
+    <row r="79" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -3271,14 +3305,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>31</v>
-      </c>
-      <c r="B80" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" t="s">
-        <v>206</v>
+      <c r="A80" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>9</v>
@@ -3295,16 +3332,16 @@
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>9</v>
@@ -3323,17 +3360,14 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>37</v>
+      <c r="A82" t="s">
+        <v>31</v>
+      </c>
+      <c r="B82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>206</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>9</v>
@@ -3353,16 +3387,16 @@
     </row>
     <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>9</v>
@@ -3382,16 +3416,16 @@
     </row>
     <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>9</v>
@@ -3409,15 +3443,18 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>5</v>
-      </c>
-      <c r="B85" t="s">
-        <v>239</v>
-      </c>
-      <c r="D85" t="s">
-        <v>238</v>
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>9</v>
@@ -3432,20 +3469,20 @@
         <v>306</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E86" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86" s="10" t="s">
         <v>9</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -3462,17 +3499,14 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>33</v>
+      <c r="A87" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" t="s">
+        <v>239</v>
+      </c>
+      <c r="D87" t="s">
+        <v>238</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>9</v>
@@ -3492,14 +3526,16 @@
     </row>
     <row r="88" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B88" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="C88" s="4" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>9</v>
@@ -3517,12 +3553,18 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>300</v>
+    <row r="89" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>9</v>
@@ -3537,18 +3579,18 @@
         <v>307</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E90" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F90" s="7" t="s">
@@ -3569,7 +3611,7 @@
         <v>279</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>9</v>
@@ -3586,18 +3628,16 @@
     </row>
     <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="B92" s="4"/>
       <c r="C92" s="4" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E92" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E92" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F92" s="7" t="s">
@@ -3614,17 +3654,11 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>22</v>
+      <c r="A93" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>293</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>9</v>
@@ -3643,11 +3677,17 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>22</v>
+      <c r="A94" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>9</v>
@@ -3666,17 +3706,17 @@
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B95" t="s">
-        <v>262</v>
-      </c>
-      <c r="C95" t="s">
-        <v>262</v>
-      </c>
-      <c r="D95" t="s">
-        <v>261</v>
+      <c r="B95" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>9</v>
@@ -3693,10 +3733,10 @@
     </row>
     <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>9</v>
@@ -3712,8 +3752,17 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" t="s">
+        <v>262</v>
+      </c>
+      <c r="C97" t="s">
+        <v>262</v>
+      </c>
       <c r="D97" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>9</v>
@@ -3729,8 +3778,11 @@
       </c>
     </row>
     <row r="98" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" t="s">
-        <v>189</v>
+      <c r="A98" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>261</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>9</v>
@@ -3746,14 +3798,11 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>319</v>
+      <c r="D99" t="s">
+        <v>188</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>321</v>
+        <v>9</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>144</v>
@@ -3762,15 +3811,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>320</v>
+    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D100" t="s">
+        <v>189</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>321</v>
+        <v>9</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>144</v>
@@ -3779,14 +3825,14 @@
         <v>322</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E101" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E101" s="10" t="s">
         <v>321</v>
       </c>
       <c r="F101" s="7" t="s">
@@ -3796,15 +3842,15 @@
         <v>322</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="E102" s="11" t="s">
-        <v>316</v>
+        <v>320</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>144</v>
@@ -3813,18 +3859,15 @@
         <v>315</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>265</v>
-      </c>
-      <c r="B103" t="s">
-        <v>266</v>
-      </c>
-      <c r="D103" t="s">
-        <v>265</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>9</v>
+    <row r="103" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>144</v>
@@ -3835,65 +3878,67 @@
     </row>
     <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>265</v>
+      </c>
+      <c r="B105" t="s">
+        <v>266</v>
+      </c>
+      <c r="D105" t="s">
+        <v>265</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G105" s="4"/>
+    </row>
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D104" s="9" t="s">
+      <c r="D106" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="E106" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D105" t="s">
+      <c r="F106" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G106" s="4"/>
+    </row>
+    <row r="107" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D107" t="s">
         <v>186</v>
       </c>
-      <c r="E105" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G105" s="4"/>
-    </row>
-    <row r="106" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D106" t="s">
+      <c r="E107" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D108" t="s">
         <v>185</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G106" s="4"/>
-    </row>
-    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D107" t="s">
-        <v>193</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E108" s="10" t="s">
+      <c r="E108" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="7" t="s">
@@ -3905,37 +3950,66 @@
     </row>
     <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
+        <v>193</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G109" s="4"/>
+    </row>
+    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D111" t="s">
         <v>187</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G109" s="4"/>
-    </row>
-    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="E111" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>309</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B112" t="s">
         <v>310</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D112" t="s">
         <v>310</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="E112" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D111" s="25"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="7"/>
+      <c r="F112" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="4:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D113" s="25"/>
+      <c r="E113" s="10"/>
+      <c r="F113" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G89" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
